--- a/artfynd/A 26954-2022 artfynd.xlsx
+++ b/artfynd/A 26954-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26954-2022 artfynd.xlsx
+++ b/artfynd/A 26954-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102940354</v>
+        <v>102944304</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>502</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ladlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium tigillare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Pers.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>640636.4991672483</v>
+        <v>640569</v>
       </c>
       <c r="R2" t="n">
-        <v>7308622.091538449</v>
+        <v>7308543</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,54 +743,40 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
+          <t>Tore Dahlberg, Frank Pollari-Karlsson, Jonathan Frendel, Iris Elmér, Linnea Backman, Melvin Lewin, Elvira Klang, Filippa Paperin, Nadja Karlsson, Elicia Olsson, Nina Wallin, Astrid Blomberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102943373</v>
+        <v>102944379</v>
       </c>
       <c r="B3" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +784,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>640865.5726088617</v>
+        <v>640438</v>
       </c>
       <c r="R3" t="n">
-        <v>7308454.205040656</v>
+        <v>7308139</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -860,54 +844,55 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elvira Klang, Tore Dahlberg, Filippa Paperin, Elicia Olsson, Frank Pollari-Karlsson, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin</t>
+          <t>Tore Dahlberg, Nadja Karlsson, Elicia Olsson, Nina Wallin, Astrid Blomberg, Filippa Paperin, Elvira Klang, Melvin Lewin, Linnea Backman, Iris Elmér, Jonathan Frendel, Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102944350</v>
+        <v>102940358</v>
       </c>
       <c r="B4" t="n">
-        <v>12274</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,43 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102016</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gropig brunbagge</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Zilora ferruginea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Paykull, 1798)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640676.3086587519</v>
+        <v>640688</v>
       </c>
       <c r="R4" t="n">
-        <v>7308638.807458507</v>
+        <v>7308634</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,55 +957,39 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Frank Pollari-Karlsson, Jonathan Frendel, Iris Elmér, Linnea Backman, Melvin Lewin, Elvira Klang, Filippa Paperin, Nadja Karlsson, Elicia Olsson, Nina Wallin, Astrid Blomberg</t>
+          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102937920</v>
+        <v>102943389</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,46 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>640574.5731479535</v>
+        <v>640443</v>
       </c>
       <c r="R5" t="n">
-        <v>7308462.439833339</v>
+        <v>7308355</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1106,19 +1054,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,27 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
+          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102940356</v>
+        <v>103045287</v>
       </c>
       <c r="B6" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,34 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>640867.8141421682</v>
+        <v>640662</v>
       </c>
       <c r="R6" t="n">
-        <v>7308517.042438567</v>
+        <v>7308619</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1218,19 +1151,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,27 +1168,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102940357</v>
+        <v>103045387</v>
       </c>
       <c r="B7" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,34 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640844.5093435711</v>
+        <v>640563</v>
       </c>
       <c r="R7" t="n">
-        <v>7308531.883957397</v>
+        <v>7308444</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1330,19 +1248,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,62 +1265,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102937919</v>
+        <v>103045405</v>
       </c>
       <c r="B8" t="n">
-        <v>57549</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208245</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640809.7872075398</v>
+        <v>640677</v>
       </c>
       <c r="R8" t="n">
-        <v>7308528.534734998</v>
+        <v>7308658</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1442,19 +1345,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,27 +1362,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102943376</v>
+        <v>103045406</v>
       </c>
       <c r="B9" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1521,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640619.5718158431</v>
+        <v>640576</v>
       </c>
       <c r="R9" t="n">
-        <v>7308624.129072166</v>
+        <v>7308533</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1554,19 +1442,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,27 +1459,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elvira Klang, Tore Dahlberg, Filippa Paperin, Elicia Olsson, Frank Pollari-Karlsson, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102943374</v>
+        <v>102940353</v>
       </c>
       <c r="B10" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,34 +1482,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>640903.4016264769</v>
+        <v>640886</v>
       </c>
       <c r="R10" t="n">
-        <v>7308552.822923549</v>
+        <v>7308519</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1666,19 +1539,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,27 +1556,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elvira Klang, Tore Dahlberg, Filippa Paperin, Elicia Olsson, Frank Pollari-Karlsson, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin</t>
+          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102944304</v>
+        <v>102940354</v>
       </c>
       <c r="B11" t="n">
-        <v>76921</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>502</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ladlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium tigillare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Pers.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1745,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>640568.5466851969</v>
+        <v>640637</v>
       </c>
       <c r="R11" t="n">
-        <v>7308543.318455496</v>
+        <v>7308622</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1778,55 +1636,39 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Frank Pollari-Karlsson, Jonathan Frendel, Iris Elmér, Linnea Backman, Melvin Lewin, Elvira Klang, Filippa Paperin, Nadja Karlsson, Elicia Olsson, Nina Wallin, Astrid Blomberg</t>
+          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>102943389</v>
+        <v>102994647</v>
       </c>
       <c r="B12" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1834,34 +1676,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640442.7751914819</v>
+        <v>640470</v>
       </c>
       <c r="R12" t="n">
-        <v>7308354.700050117</v>
+        <v>7308214</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1891,19 +1733,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,27 +1750,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elvira Klang, Tore Dahlberg, Filippa Paperin, Elicia Olsson, Frank Pollari-Karlsson, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin</t>
+          <t>Tore Dahlberg, Nina Wallin, Filippa Paperin, Frank Pollari-Karlsson, Elicia Olsson, Elvira Klang, Astrid Blomberg, Melvin Lewin, Nadja Karlsson, Iris Elmér, Linnea Backman, Jonathan Frendel</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>102940353</v>
+        <v>103045192</v>
       </c>
       <c r="B13" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,14 +1793,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>640885.749157311</v>
+        <v>640509</v>
       </c>
       <c r="R13" t="n">
-        <v>7308519.565568142</v>
+        <v>7308241</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2003,19 +1830,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,27 +1847,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102940355</v>
+        <v>103045194</v>
       </c>
       <c r="B14" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2058,34 +1870,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>640870.3785329926</v>
+        <v>640663</v>
       </c>
       <c r="R14" t="n">
-        <v>7308473.300940692</v>
+        <v>7308616</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2115,19 +1927,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,27 +1944,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102944361</v>
+        <v>102937920</v>
       </c>
       <c r="B15" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,34 +1967,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>641014.6679912611</v>
+        <v>640574</v>
       </c>
       <c r="R15" t="n">
-        <v>7308452.120787187</v>
+        <v>7308462</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2227,19 +2036,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2254,27 +2053,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Frank Pollari-Karlsson, Jonathan Frendel, Iris Elmér, Linnea Backman, Melvin Lewin, Elvira Klang, Filippa Paperin, Nadja Karlsson, Elicia Olsson, Nina Wallin, Astrid Blomberg</t>
+          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102994647</v>
+        <v>102944350</v>
       </c>
       <c r="B16" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12389</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2282,34 +2076,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>102016</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gropig brunbagge</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Zilora ferruginea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Paykull, 1798)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>640469.7873973949</v>
+        <v>640676</v>
       </c>
       <c r="R16" t="n">
-        <v>7308214.165223241</v>
+        <v>7308639</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2339,27 +2142,18 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2371,22 +2165,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Nina Wallin, Filippa Paperin, Frank Pollari-Karlsson, Elicia Olsson, Elvira Klang, Astrid Blomberg, Melvin Lewin, Nadja Karlsson, Iris Elmér, Linnea Backman, Jonathan Frendel</t>
+          <t>Tore Dahlberg, Frank Pollari-Karlsson, Jonathan Frendel, Iris Elmér, Linnea Backman, Melvin Lewin, Elvira Klang, Filippa Paperin, Nadja Karlsson, Elicia Olsson, Nina Wallin, Astrid Blomberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103045406</v>
+        <v>102937936</v>
       </c>
       <c r="B17" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2394,34 +2183,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6437</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>640575.6001827475</v>
+        <v>640484</v>
       </c>
       <c r="R17" t="n">
-        <v>7308533.415851056</v>
+        <v>7308216</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2451,19 +2252,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2478,27 +2269,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103045220</v>
+        <v>102937937</v>
       </c>
       <c r="B18" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,34 +2292,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>640842.1533152735</v>
+        <v>640572</v>
       </c>
       <c r="R18" t="n">
-        <v>7308504.709575765</v>
+        <v>7308557</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2563,19 +2349,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2590,27 +2366,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103045287</v>
+        <v>102937940</v>
       </c>
       <c r="B19" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,34 +2389,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>640662.5345611293</v>
+        <v>640684</v>
       </c>
       <c r="R19" t="n">
-        <v>7308618.452164819</v>
+        <v>7308642</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2675,19 +2446,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,62 +2463,66 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103045194</v>
+        <v>102944111</v>
       </c>
       <c r="B20" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>640663.4941946714</v>
+        <v>640498</v>
       </c>
       <c r="R20" t="n">
-        <v>7308615.629642215</v>
+        <v>7308384</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2787,89 +2552,90 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Jonathan Frendel, Linnea Backman, Astrid Blomberg, Elvira Klang, Nina Wallin, Nadja Karlsson, Elicia Olsson, Melvin Lewin, Filippa Paperin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103045387</v>
+        <v>102937919</v>
       </c>
       <c r="B21" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>208245</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>640562.7442344732</v>
+        <v>640810</v>
       </c>
       <c r="R21" t="n">
-        <v>7308444.229435626</v>
+        <v>7308528</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2899,19 +2665,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2926,62 +2682,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103045219</v>
+        <v>102937931</v>
       </c>
       <c r="B22" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>640866.8677575086</v>
+        <v>640827</v>
       </c>
       <c r="R22" t="n">
-        <v>7308511.256165458</v>
+        <v>7308454</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3011,54 +2762,40 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103045221</v>
+        <v>102940355</v>
       </c>
       <c r="B23" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,14 +2823,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>640810.5992769126</v>
+        <v>640870</v>
       </c>
       <c r="R23" t="n">
-        <v>7308520.375224576</v>
+        <v>7308473</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3123,19 +2860,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,27 +2877,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103045192</v>
+        <v>102940356</v>
       </c>
       <c r="B24" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3178,34 +2900,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>640509.5309017432</v>
+        <v>640868</v>
       </c>
       <c r="R24" t="n">
-        <v>7308240.71749665</v>
+        <v>7308517</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3235,19 +2957,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3262,27 +2974,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103045222</v>
+        <v>102940357</v>
       </c>
       <c r="B25" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,14 +3017,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>640564.9672576364</v>
+        <v>640845</v>
       </c>
       <c r="R25" t="n">
-        <v>7308524.283994117</v>
+        <v>7308532</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3347,19 +3054,9 @@
           <t>2022-08-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-08-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3374,15 +3071,985 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
+          <t>Jonathan Frendel</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>102943373</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>640866</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7308454</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>102943374</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>640903</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7308553</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>102943375</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>640887</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7308563</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>102943376</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>640619</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7308624</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>103045217</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>640470</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7308299</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
           <t>Linnea Backman</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>Linnea Backman</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>103045218</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>640466</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7308334</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>103045219</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>640867</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7308511</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>103045220</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>640842</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7308505</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>103045221</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>640811</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7308520</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>103045222</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>640565</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7308524</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26954-2022 artfynd.xlsx
+++ b/artfynd/A 26954-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102944304</v>
+        <v>135294705</v>
       </c>
       <c r="B2" t="n">
-        <v>78742</v>
+        <v>92220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>502</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ladlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium tigillare</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Pers.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>640569</v>
+        <v>640689</v>
       </c>
       <c r="R2" t="n">
-        <v>7308543</v>
+        <v>7308553</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,29 +764,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Frank Pollari-Karlsson, Jonathan Frendel, Iris Elmér, Linnea Backman, Melvin Lewin, Elvira Klang, Filippa Paperin, Nadja Karlsson, Elicia Olsson, Nina Wallin, Astrid Blomberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102944379</v>
+        <v>135294703</v>
       </c>
       <c r="B3" t="n">
-        <v>83173</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -784,40 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>640438</v>
+        <v>640691</v>
       </c>
       <c r="R3" t="n">
-        <v>7308139</v>
+        <v>7308552</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -841,12 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -855,44 +875,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Nadja Karlsson, Elicia Olsson, Nina Wallin, Astrid Blomberg, Filippa Paperin, Elvira Klang, Melvin Lewin, Linnea Backman, Iris Elmér, Jonathan Frendel, Frank Pollari-Karlsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102940358</v>
+        <v>135294864</v>
       </c>
       <c r="B4" t="n">
-        <v>91962</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +932,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640688</v>
+        <v>640577</v>
       </c>
       <c r="R4" t="n">
-        <v>7308634</v>
+        <v>7308336</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +962,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +992,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102943389</v>
+        <v>102944304</v>
       </c>
       <c r="B5" t="n">
-        <v>91962</v>
+        <v>78742</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +1019,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>502</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ladlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium tigillare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Pers.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>640443</v>
+        <v>640569</v>
       </c>
       <c r="R5" t="n">
-        <v>7308355</v>
+        <v>7308543</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1065,28 +1087,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
+          <t>Tore Dahlberg, Frank Pollari-Karlsson, Jonathan Frendel, Iris Elmér, Linnea Backman, Melvin Lewin, Elvira Klang, Filippa Paperin, Nadja Karlsson, Elicia Olsson, Nina Wallin, Astrid Blomberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103045287</v>
+        <v>135293596</v>
       </c>
       <c r="B6" t="n">
-        <v>93189</v>
+        <v>78788</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,37 +1117,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>502</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ladlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Calicium tigillare</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Pers.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>640662</v>
+        <v>640553</v>
       </c>
       <c r="R6" t="n">
-        <v>7308619</v>
+        <v>7308542</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,12 +1174,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>stolpe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1164,26 +1205,40 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stolpe, trägärdesgård mm</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Post/wooden fences etc. # gammal stock, används numera som stolpe</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Alva Danielsson, Benny Öwre, Ulrika Karlsson, Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103045387</v>
+        <v>135294863</v>
       </c>
       <c r="B7" t="n">
-        <v>93191</v>
+        <v>81355</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,37 +1246,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>640563</v>
+        <v>640568</v>
       </c>
       <c r="R7" t="n">
-        <v>7308444</v>
+        <v>7308347</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,12 +1300,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,22 +1330,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103045405</v>
+        <v>135294885</v>
       </c>
       <c r="B8" t="n">
-        <v>78730</v>
+        <v>81355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,37 +1357,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>640677</v>
+        <v>640437</v>
       </c>
       <c r="R8" t="n">
-        <v>7308658</v>
+        <v>7308365</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,12 +1411,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,22 +1441,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103045406</v>
+        <v>102944379</v>
       </c>
       <c r="B9" t="n">
-        <v>78730</v>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,34 +1468,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>640576</v>
+        <v>640438</v>
       </c>
       <c r="R9" t="n">
-        <v>7308533</v>
+        <v>7308139</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1453,28 +1539,44 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Tore Dahlberg, Nadja Karlsson, Elicia Olsson, Nina Wallin, Astrid Blomberg, Filippa Paperin, Elvira Klang, Melvin Lewin, Linnea Backman, Iris Elmér, Jonathan Frendel, Frank Pollari-Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102940354</v>
+        <v>135294878</v>
       </c>
       <c r="B10" t="n">
-        <v>79946</v>
+        <v>83222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,37 +1584,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>640637</v>
+        <v>640438</v>
       </c>
       <c r="R10" t="n">
-        <v>7308622</v>
+        <v>7308199</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,12 +1641,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1550,28 +1665,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102994647</v>
+        <v>102940358</v>
       </c>
       <c r="B11" t="n">
-        <v>79946</v>
+        <v>91962</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>640470</v>
+        <v>640688</v>
       </c>
       <c r="R11" t="n">
-        <v>7308214</v>
+        <v>7308634</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1653,22 +1773,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Jonathan Frendel</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Nina Wallin, Filippa Paperin, Frank Pollari-Karlsson, Elicia Olsson, Elvira Klang, Astrid Blomberg, Melvin Lewin, Nadja Karlsson, Iris Elmér, Linnea Backman, Jonathan Frendel</t>
+          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103045192</v>
+        <v>102943389</v>
       </c>
       <c r="B12" t="n">
-        <v>79946</v>
+        <v>91962</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1796,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>640509</v>
+        <v>640443</v>
       </c>
       <c r="R12" t="n">
-        <v>7308241</v>
+        <v>7308355</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1750,60 +1870,63 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103045194</v>
+        <v>135294214</v>
       </c>
       <c r="B13" t="n">
-        <v>79946</v>
+        <v>92370</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4217</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Västra Kikkejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>640663</v>
+        <v>640468</v>
       </c>
       <c r="R13" t="n">
-        <v>7308616</v>
+        <v>7308226</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,12 +1950,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1841,28 +1974,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>102937920</v>
+        <v>103045287</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>93189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,46 +2008,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>640574</v>
+        <v>640662</v>
       </c>
       <c r="R14" t="n">
-        <v>7308462</v>
+        <v>7308619</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -1956,22 +2082,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>102944350</v>
+        <v>103045387</v>
       </c>
       <c r="B15" t="n">
-        <v>12389</v>
+        <v>93191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,43 +2105,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102016</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gropig brunbagge</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Zilora ferruginea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Paykull, 1798)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>640676</v>
+        <v>640563</v>
       </c>
       <c r="R15" t="n">
-        <v>7308639</v>
+        <v>7308444</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2056,79 +2173,66 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Frank Pollari-Karlsson, Jonathan Frendel, Iris Elmér, Linnea Backman, Melvin Lewin, Elvira Klang, Filippa Paperin, Nadja Karlsson, Elicia Olsson, Nina Wallin, Astrid Blomberg</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>102937936</v>
+        <v>135294212</v>
       </c>
       <c r="B16" t="n">
-        <v>58057</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Västra Kikkejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>640484</v>
+        <v>640486</v>
       </c>
       <c r="R16" t="n">
-        <v>7308216</v>
+        <v>7308240</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2152,12 +2256,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2172,60 +2286,60 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>102937937</v>
+        <v>135294704</v>
       </c>
       <c r="B17" t="n">
-        <v>58057</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>640572</v>
+        <v>640686</v>
       </c>
       <c r="R17" t="n">
-        <v>7308557</v>
+        <v>7308559</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2249,12 +2363,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2269,60 +2393,64 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102937940</v>
+        <v>135294870</v>
       </c>
       <c r="B18" t="n">
-        <v>58057</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>640684</v>
+        <v>640483</v>
       </c>
       <c r="R18" t="n">
-        <v>7308642</v>
+        <v>7308230</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2346,12 +2474,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2360,72 +2498,68 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102944111</v>
+        <v>103045405</v>
       </c>
       <c r="B19" t="n">
-        <v>5199</v>
+        <v>78730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>640498</v>
+        <v>640677</v>
       </c>
       <c r="R19" t="n">
-        <v>7308384</v>
+        <v>7308658</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2466,44 +2600,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Jonathan Frendel, Linnea Backman, Astrid Blomberg, Elvira Klang, Nina Wallin, Nadja Karlsson, Elicia Olsson, Melvin Lewin, Filippa Paperin</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102943376</v>
+        <v>103045406</v>
       </c>
       <c r="B20" t="n">
-        <v>79917</v>
+        <v>78730</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2511,21 +2629,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2653,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>640619</v>
+        <v>640576</v>
       </c>
       <c r="R20" t="n">
-        <v>7308624</v>
+        <v>7308533</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2585,22 +2703,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103045217</v>
+        <v>135294217</v>
       </c>
       <c r="B21" t="n">
-        <v>79917</v>
+        <v>78776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2608,37 +2726,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Västra Kikkejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>640470</v>
+        <v>640434</v>
       </c>
       <c r="R21" t="n">
-        <v>7308299</v>
+        <v>7308159</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2662,12 +2783,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2676,28 +2807,33 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103045218</v>
+        <v>135294861</v>
       </c>
       <c r="B22" t="n">
-        <v>79917</v>
+        <v>78776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2705,37 +2841,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>640466</v>
+        <v>640568</v>
       </c>
       <c r="R22" t="n">
-        <v>7308334</v>
+        <v>7308347</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2759,12 +2895,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2779,22 +2925,26 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103045222</v>
+        <v>135294866</v>
       </c>
       <c r="B23" t="n">
-        <v>79917</v>
+        <v>78776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,37 +2952,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>640565</v>
+        <v>640583</v>
       </c>
       <c r="R23" t="n">
-        <v>7308524</v>
+        <v>7308280</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2856,12 +3006,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2876,22 +3036,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>102940353</v>
+        <v>135295272</v>
       </c>
       <c r="B24" t="n">
-        <v>79946</v>
+        <v>78776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2899,37 +3063,40 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>640886</v>
+        <v>640472</v>
       </c>
       <c r="R24" t="n">
-        <v>7308519</v>
+        <v>7308320</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2953,12 +3120,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2967,50 +3144,55 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102937919</v>
+        <v>135294860</v>
       </c>
       <c r="B25" t="n">
-        <v>58790</v>
+        <v>83358</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208245</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3020,13 +3202,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>640810</v>
+        <v>640532</v>
       </c>
       <c r="R25" t="n">
-        <v>7308528</v>
+        <v>7308372</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3050,12 +3232,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3070,60 +3262,64 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>102937931</v>
+        <v>135295266</v>
       </c>
       <c r="B26" t="n">
-        <v>97989</v>
+        <v>83358</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>640827</v>
+        <v>640558</v>
       </c>
       <c r="R26" t="n">
-        <v>7308454</v>
+        <v>7308391</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3147,12 +3343,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3161,29 +3367,32 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>102940355</v>
+        <v>102940354</v>
       </c>
       <c r="B27" t="n">
-        <v>79917</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3191,21 +3400,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3215,10 +3424,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>640870</v>
+        <v>640637</v>
       </c>
       <c r="R27" t="n">
-        <v>7308473</v>
+        <v>7308622</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3277,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>102940356</v>
+        <v>102994647</v>
       </c>
       <c r="B28" t="n">
-        <v>79917</v>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,21 +3497,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3312,10 +3521,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>640868</v>
+        <v>640470</v>
       </c>
       <c r="R28" t="n">
-        <v>7308517</v>
+        <v>7308214</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3362,22 +3571,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
+          <t>Tore Dahlberg, Nina Wallin, Filippa Paperin, Frank Pollari-Karlsson, Elicia Olsson, Elvira Klang, Astrid Blomberg, Melvin Lewin, Nadja Karlsson, Iris Elmér, Linnea Backman, Jonathan Frendel</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>102940357</v>
+        <v>103045192</v>
       </c>
       <c r="B29" t="n">
-        <v>79917</v>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3385,34 +3594,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>640845</v>
+        <v>640509</v>
       </c>
       <c r="R29" t="n">
-        <v>7308532</v>
+        <v>7308241</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3459,22 +3668,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jonathan Frendel</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>102943373</v>
+        <v>103045194</v>
       </c>
       <c r="B30" t="n">
-        <v>79917</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3482,21 +3691,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3506,10 +3715,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>640866</v>
+        <v>640663</v>
       </c>
       <c r="R30" t="n">
-        <v>7308454</v>
+        <v>7308616</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3556,22 +3765,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
+          <t>Linnea Backman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>102943374</v>
+        <v>135293595</v>
       </c>
       <c r="B31" t="n">
-        <v>79917</v>
+        <v>79992</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3579,37 +3788,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>640903</v>
+        <v>640657</v>
       </c>
       <c r="R31" t="n">
-        <v>7308553</v>
+        <v>7308631</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3633,12 +3845,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3653,22 +3875,26 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Alva Danielsson, Elin Kannerby, Anton Lundberg, Jörgen Sundin, Tyr Nilsson, Alva Dahlqvist Cederstrand, per-erik mukka, Martin Axegård, Ulrika Karlsson, Benny Öwre, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>102943375</v>
+        <v>135294211</v>
       </c>
       <c r="B32" t="n">
-        <v>79917</v>
+        <v>79992</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3676,37 +3902,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Västra Kikkejaure, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>640887</v>
+        <v>640475</v>
       </c>
       <c r="R32" t="n">
-        <v>7308563</v>
+        <v>7308203</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3730,12 +3956,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3750,22 +3986,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>103045219</v>
+        <v>135294862</v>
       </c>
       <c r="B33" t="n">
-        <v>79917</v>
+        <v>79992</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3773,37 +4009,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>640867</v>
+        <v>640568</v>
       </c>
       <c r="R33" t="n">
-        <v>7308511</v>
+        <v>7308347</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3827,12 +4063,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3847,22 +4093,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>103045220</v>
+        <v>135294865</v>
       </c>
       <c r="B34" t="n">
-        <v>79917</v>
+        <v>79992</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3870,37 +4120,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>640842</v>
+        <v>640583</v>
       </c>
       <c r="R34" t="n">
-        <v>7308505</v>
+        <v>7308280</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3924,12 +4174,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3944,22 +4204,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linnea Backman</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>103045221</v>
+        <v>135294868</v>
       </c>
       <c r="B35" t="n">
-        <v>79917</v>
+        <v>79992</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3967,37 +4231,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Strávkajávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>640811</v>
+        <v>640507</v>
       </c>
       <c r="R35" t="n">
-        <v>7308520</v>
+        <v>7308240</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4021,12 +4285,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-08-09</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4041,15 +4315,6572 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135294872</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>640464</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7308207</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135295269</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>640450</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7308181</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135295271</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>640472</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7308320</v>
+      </c>
+      <c r="S38" t="n">
+        <v>14</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>102937920</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>640574</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7308462</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135302458</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>640672</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7308633</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Jörgen Sundin, Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>102944350</v>
+      </c>
+      <c r="B41" t="n">
+        <v>12389</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>102016</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gropig brunbagge</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Zilora ferruginea</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Paykull, 1798)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>640676</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7308639</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Frank Pollari-Karlsson, Jonathan Frendel, Iris Elmér, Linnea Backman, Melvin Lewin, Elvira Klang, Filippa Paperin, Nadja Karlsson, Elicia Olsson, Nina Wallin, Astrid Blomberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>102937936</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>640484</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7308216</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>102937937</v>
+      </c>
+      <c r="B43" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>640572</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7308557</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>102937940</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>640684</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7308642</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>102944111</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>640498</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7308384</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Jonathan Frendel, Linnea Backman, Astrid Blomberg, Elvira Klang, Nina Wallin, Nadja Karlsson, Elicia Olsson, Melvin Lewin, Filippa Paperin</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135294216</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Västra Kikkejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>640429</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7308180</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135294210</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Västra Kikkejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>640511</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7308398</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>102943376</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>640619</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7308624</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>103045217</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>640470</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7308299</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
           <t>Linnea Backman</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AX49" t="inlineStr">
         <is>
           <t>Linnea Backman</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>103045218</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>640466</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7308334</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>103045222</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>640565</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7308524</v>
+      </c>
+      <c r="S51" t="n">
+        <v>15</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135294875</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>640449</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7308185</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135295273</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>640472</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7308320</v>
+      </c>
+      <c r="S53" t="n">
+        <v>14</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135293594</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>640665</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7308628</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, Anton Lundberg, Jörgen Sundin, Tyr Nilsson, Alva Dahlqvist Cederstrand, per-erik mukka, Martin Axegård, Ulrika Karlsson, Benny Öwre, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135294219</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Västra Kikkejaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>640464</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7308267</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135294859</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>640502</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7308394</v>
+      </c>
+      <c r="S56" t="n">
+        <v>11</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135294873</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>640465</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7308198</v>
+      </c>
+      <c r="S57" t="n">
+        <v>8</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135295267</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>640592</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7308320</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135294880</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80267</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>640470</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7308297</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135294884</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80267</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>640461</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7308305</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På kelostubbe på skogsbevuxen myr</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135293592</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>353</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>640868</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7308500</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, Anton Lundberg, Jörgen Sundin, Tyr Nilsson, Alva Dahlqvist Cederstrand, per-erik mukka, Martin Axegård, Ulrika Karlsson, Benny Öwre, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135294683</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>353</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>641028</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7308439</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135294679</v>
+      </c>
+      <c r="B63" t="n">
+        <v>81355</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>640940</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7308410</v>
+      </c>
+      <c r="S63" t="n">
+        <v>17</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135294695</v>
+      </c>
+      <c r="B64" t="n">
+        <v>81355</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>640978</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7308491</v>
+      </c>
+      <c r="S64" t="n">
+        <v>11</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135294689</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92027</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>641024</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7308467</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135294687</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91896</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>641031</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7308484</v>
+      </c>
+      <c r="S66" t="n">
+        <v>12</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135294701</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>640832</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7308511</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135302459</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>640950</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7308532</v>
+      </c>
+      <c r="S68" t="n">
+        <v>13</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Jörgen Sundin, Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>102940353</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>640886</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7308519</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Jonathan Frendel</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135294692</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>641009</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7308495</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135294702</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>640832</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7308507</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135302461</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>640963</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7308509</v>
+      </c>
+      <c r="S72" t="n">
+        <v>22</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Jörgen Sundin, Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135302462</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>640990</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7308378</v>
+      </c>
+      <c r="S73" t="n">
+        <v>31</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Jörgen Sundin, Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135302460</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>640945</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7308531</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson, Jörgen Sundin, Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135293589</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>640974</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7308433</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>nytt bohål, grantickegranstubbe även ett till bohål, något större i diameter, på andra sidan av stammen</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, Jörgen Sundin, Tyr Nilsson, per-erik mukka, Benny Öwre, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135293591</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>640952</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7308520</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, Anton Lundberg, Jörgen Sundin, Tyr Nilsson, Alva Dahlqvist Cederstrand, per-erik mukka, Martin Axegård, Ulrika Karlsson, Benny Öwre, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>102937919</v>
+      </c>
+      <c r="B77" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>640810</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7308528</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135294682</v>
+      </c>
+      <c r="B78" t="n">
+        <v>41606</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>215713</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Grå blåbärsfältmätare</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Entephria caesiata</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>641015</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7308442</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>102937931</v>
+      </c>
+      <c r="B79" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>640827</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7308454</v>
+      </c>
+      <c r="S79" t="n">
+        <v>15</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Frank Pollari-Karlsson, Astrid Blomberg, Elicia Olsson, Elvira Klang, Filippa Paperin, Iris Elmér, Jonathan Frendel, Linnea Backman, Melvin Lewin, Nadja Karlsson, Nina Wallin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>102940355</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>640870</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7308473</v>
+      </c>
+      <c r="S80" t="n">
+        <v>15</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Jonathan Frendel</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>102940356</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>640868</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7308517</v>
+      </c>
+      <c r="S81" t="n">
+        <v>15</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Jonathan Frendel</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>102940357</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>640845</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7308532</v>
+      </c>
+      <c r="S82" t="n">
+        <v>15</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Jonathan Frendel</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Jonathan Frendel, Tore Dahlberg, Frank Pollari-Karlsson, Iris Elmér, Linnea Backman, Elvira Klang, Filippa Paperin, Astrid Blomberg, Nadja Karlsson, Nina Wallin, Melvin Lewin, Elicia Olsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>102943373</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>640866</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7308454</v>
+      </c>
+      <c r="S83" t="n">
+        <v>15</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>102943374</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>640903</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7308553</v>
+      </c>
+      <c r="S84" t="n">
+        <v>15</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>102943375</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>640887</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7308563</v>
+      </c>
+      <c r="S85" t="n">
+        <v>15</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Elvira Klang, Nina Wallin, Nadja Karlsson, Melvin Lewin, Linnea Backman, Jonathan Frendel, Iris Elmér, Frank Pollari-Karlsson, Elicia Olsson, Filippa Paperin, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>103045219</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>640867</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7308511</v>
+      </c>
+      <c r="S86" t="n">
+        <v>15</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>103045220</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>640842</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7308505</v>
+      </c>
+      <c r="S87" t="n">
+        <v>15</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>103045221</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>..., Pi lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>640811</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7308520</v>
+      </c>
+      <c r="S88" t="n">
+        <v>15</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2022-08-09</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Linnea Backman</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135293593</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>640862</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7308525</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, Anton Lundberg, Jörgen Sundin, Tyr Nilsson, Alva Dahlqvist Cederstrand, per-erik mukka, Martin Axegård, Ulrika Karlsson, Benny Öwre, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135294678</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>640940</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7308411</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135294684</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>641024</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7308447</v>
+      </c>
+      <c r="S91" t="n">
+        <v>8</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135294694</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>640981</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7308509</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135294697</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>640897</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7308481</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135294700</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>640831</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7308512</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135293590</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Strávkajávrrie, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>641001</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7308458</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby, Anton Lundberg, Jörgen Sundin, Tyr Nilsson, Alva Dahlqvist Cederstrand, per-erik mukka, Martin Axegård, Ulrika Karlsson, Benny Öwre, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>135294685</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Tis Gr 2_Västra Kikkejaure Rengärdet avvanm_prio 2_orto, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>641030</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7308481</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Jörgen Sundin, Elin Kannerby, Tyr Nilsson, Benny Öwre, per-erik mukka, anders tedeholm, Christina Boyd, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26954-2022 artfynd.xlsx
+++ b/artfynd/A 26954-2022 artfynd.xlsx
@@ -928,7 +928,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1266,7 +1266,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1377,7 +1377,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1607,7 +1607,7 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -2861,7 +2861,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -2972,7 +2972,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -3198,7 +3198,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -4029,7 +4029,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -4140,7 +4140,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
@@ -4251,7 +4251,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
@@ -4362,7 +4362,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -6071,7 +6071,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
@@ -6526,7 +6526,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -6637,7 +6637,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
@@ -6854,7 +6854,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -6960,7 +6960,7 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Strávkajávrrie, Pi lm</t>
+          <t>Tis Gr 2 Västra Kikkejaure Rengärdet avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">

--- a/artfynd/A 26954-2022 artfynd.xlsx
+++ b/artfynd/A 26954-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294705</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294703</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294864</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102944304</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293596</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294863</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1452,6 +1487,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294885</t>
         </is>
       </c>
     </row>
@@ -1570,6 +1610,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102944379</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1685,6 +1730,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294878</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102940358</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1879,6 +1934,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102943389</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1994,6 +2054,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294214</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2091,6 +2156,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045287</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2188,6 +2258,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045387</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2295,6 +2370,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294212</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2406,6 +2486,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294704</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2518,6 +2603,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294870</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2615,6 +2705,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045405</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2712,6 +2807,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045406</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2827,6 +2927,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294217</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2938,6 +3043,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294861</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3047,6 +3157,11 @@
       <c r="AY23" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294866</t>
         </is>
       </c>
     </row>
@@ -3164,6 +3279,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295272</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3275,6 +3395,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294860</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3386,6 +3511,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295266</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3483,6 +3613,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102940354</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3580,6 +3715,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102994647</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3677,6 +3817,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045192</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3774,6 +3919,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045194</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3888,6 +4038,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293595</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3995,6 +4150,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294211</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4106,6 +4266,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294862</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4217,6 +4382,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294865</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4328,6 +4498,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294868</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4439,6 +4614,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294872</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4548,6 +4728,11 @@
       <c r="AY37" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295269</t>
         </is>
       </c>
     </row>
@@ -4665,6 +4850,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295271</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4774,6 +4964,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102937920</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4894,6 +5089,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302458</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5001,6 +5201,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102944350</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5110,6 +5315,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102937936</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5207,6 +5417,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102937937</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5304,6 +5519,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102937940</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5426,6 +5646,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102944111</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5542,6 +5767,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294216</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5649,6 +5879,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294210</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5746,6 +5981,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102943376</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5843,6 +6083,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045217</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5940,6 +6185,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045218</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6037,6 +6287,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045222</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6140,12 +6395,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294875</t>
         </is>
       </c>
     </row>
@@ -6263,6 +6523,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295273</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6377,6 +6642,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293594</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6492,6 +6762,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294219</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6603,6 +6878,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294859</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6714,6 +6994,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294873</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6825,6 +7110,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135295267</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6931,6 +7221,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294880</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7040,6 +7335,11 @@
       <c r="AY60" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294884</t>
         </is>
       </c>
     </row>
@@ -7156,6 +7456,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293592</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7267,6 +7572,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294683</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7378,6 +7688,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294679</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7489,6 +7804,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294695</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7600,6 +7920,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294689</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7711,6 +8036,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294687</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7822,6 +8152,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294701</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7929,6 +8264,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302459</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8026,6 +8366,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102940353</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8137,6 +8482,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294692</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8248,6 +8598,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294702</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8355,6 +8710,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302461</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8462,6 +8822,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302462</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8569,6 +8934,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135302460</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8689,6 +9059,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293589</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8808,6 +9183,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293591</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8905,6 +9285,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102937919</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9016,6 +9401,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294682</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9114,6 +9504,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102937931</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9211,6 +9606,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102940355</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9308,6 +9708,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102940356</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9405,6 +9810,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102940357</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9502,6 +9912,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102943373</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9599,6 +10014,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102943374</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9696,6 +10116,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102943375</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9793,6 +10218,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045219</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9890,6 +10320,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045220</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9987,6 +10422,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103045221</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10101,6 +10541,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293593</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10212,6 +10657,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294678</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10323,6 +10773,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294684</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10434,6 +10889,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294694</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10545,6 +11005,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294697</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10654,6 +11119,11 @@
       <c r="AY94" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294700</t>
         </is>
       </c>
     </row>
@@ -10770,6 +11240,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293590</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10881,8 +11356,110 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135294685</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26954-2022 artfynd.xlsx
+++ b/artfynd/A 26954-2022 artfynd.xlsx
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">

--- a/artfynd/A 26954-2022 artfynd.xlsx
+++ b/artfynd/A 26954-2022 artfynd.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson</t>
+          <t>anders tedeholm, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
+          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson</t>
+          <t>anders tedeholm, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
+          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">

--- a/artfynd/A 26954-2022 artfynd.xlsx
+++ b/artfynd/A 26954-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294705</v>
       </c>
       <c r="B2" t="n">
-        <v>92220</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135294703</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135294864</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1134,7 +1134,7 @@
         <v>135293596</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>78826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135294863</v>
       </c>
       <c r="B7" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1384,7 +1384,7 @@
         <v>135294885</v>
       </c>
       <c r="B8" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1621,7 +1621,7 @@
         <v>135294878</v>
       </c>
       <c r="B10" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1945,7 +1945,7 @@
         <v>135294214</v>
       </c>
       <c r="B13" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>135294212</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>135294704</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>135294870</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>135294217</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>135294861</v>
       </c>
       <c r="B22" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3054,7 +3054,7 @@
         <v>135294866</v>
       </c>
       <c r="B23" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3170,7 +3170,7 @@
         <v>135295272</v>
       </c>
       <c r="B24" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>anders tedeholm, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3290,7 +3290,7 @@
         <v>135294860</v>
       </c>
       <c r="B25" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3406,7 +3406,7 @@
         <v>135295266</v>
       </c>
       <c r="B26" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>anders tedeholm, Anton Lundberg, Martin Axegård, Alva Dahlqvist Cederstrand, Ulrika Karlsson, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson, Ulrika Karlsson, Alva Dahlqvist Cederstrand, Martin Axegård, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3930,7 +3930,7 @@
         <v>135293595</v>
       </c>
       <c r="B31" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>135294211</v>
       </c>
       <c r="B32" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>135294862</v>
       </c>
       <c r="B33" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4277,7 +4277,7 @@
         <v>135294865</v>
       </c>
       <c r="B34" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4393,7 +4393,7 @@
         <v>135294868</v>
       </c>
       <c r="B35" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4509,7 +4509,7 @@
         <v>135294872</v>
       </c>
       <c r="B36" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4625,7 +4625,7 @@
         <v>135295269</v>
       </c>
       <c r="B37" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>135295271</v>
       </c>
       <c r="B38" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>135302458</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>135294216</v>
       </c>
       <c r="B46" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>135294210</v>
       </c>
       <c r="B47" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>135294875</v>
       </c>
       <c r="B52" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -6414,7 +6414,7 @@
         <v>135295273</v>
       </c>
       <c r="B53" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>anders tedeholm, Alva Danielsson, per-erik mukka, Jörgen Sundin, Tyr Nilsson, Elin Kannerby, Christina Boyd, Benny Öwre</t>
+          <t>anders tedeholm, Benny Öwre, Christina Boyd, Elin Kannerby, Tyr Nilsson, Jörgen Sundin, per-erik mukka, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6534,7 +6534,7 @@
         <v>135293594</v>
       </c>
       <c r="B54" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>135294219</v>
       </c>
       <c r="B55" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>135294859</v>
       </c>
       <c r="B56" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6889,7 +6889,7 @@
         <v>135294873</v>
       </c>
       <c r="B57" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -7005,7 +7005,7 @@
         <v>135295267</v>
       </c>
       <c r="B58" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>135294880</v>
       </c>
       <c r="B59" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -7232,7 +7232,7 @@
         <v>135294884</v>
       </c>
       <c r="B60" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, per-erik mukka, Christina Boyd, anders tedeholm</t>
+          <t>Tyr Nilsson, anders tedeholm, Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7348,7 +7348,7 @@
         <v>135293592</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>135294683</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>135294679</v>
       </c>
       <c r="B63" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>135294695</v>
       </c>
       <c r="B64" t="n">
-        <v>81355</v>
+        <v>81393</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135294689</v>
       </c>
       <c r="B65" t="n">
-        <v>92027</v>
+        <v>92069</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>135294687</v>
       </c>
       <c r="B66" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>135294701</v>
       </c>
       <c r="B67" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135302459</v>
       </c>
       <c r="B68" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>135294692</v>
       </c>
       <c r="B70" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>135294702</v>
       </c>
       <c r="B71" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>135302461</v>
       </c>
       <c r="B72" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>135302462</v>
       </c>
       <c r="B73" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>135302460</v>
       </c>
       <c r="B74" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>135293589</v>
       </c>
       <c r="B75" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>135293591</v>
       </c>
       <c r="B76" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>135294682</v>
       </c>
       <c r="B78" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>135293593</v>
       </c>
       <c r="B89" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>135294678</v>
       </c>
       <c r="B90" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>135294684</v>
       </c>
       <c r="B91" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>135294694</v>
       </c>
       <c r="B92" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>135294697</v>
       </c>
       <c r="B93" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>135294700</v>
       </c>
       <c r="B94" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>135293590</v>
       </c>
       <c r="B95" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135294685</v>
       </c>
       <c r="B96" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 26954-2022 artfynd.xlsx
+++ b/artfynd/A 26954-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294705</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135294703</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135294864</v>
       </c>
       <c r="B4" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>135293596</v>
       </c>
       <c r="B6" t="n">
-        <v>78826</v>
+        <v>78853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135294863</v>
       </c>
       <c r="B7" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>135294885</v>
       </c>
       <c r="B8" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>135294878</v>
       </c>
       <c r="B10" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>135294214</v>
       </c>
       <c r="B13" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>135294212</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>135294704</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>135294870</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>135294217</v>
       </c>
       <c r="B21" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>135294861</v>
       </c>
       <c r="B22" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>135294866</v>
       </c>
       <c r="B23" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>135295272</v>
       </c>
       <c r="B24" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>135294860</v>
       </c>
       <c r="B25" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>135295266</v>
       </c>
       <c r="B26" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>135293595</v>
       </c>
       <c r="B31" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>135294211</v>
       </c>
       <c r="B32" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>135294862</v>
       </c>
       <c r="B33" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         <v>135294865</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>135294868</v>
       </c>
       <c r="B35" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>135294872</v>
       </c>
       <c r="B36" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>135295269</v>
       </c>
       <c r="B37" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>135295271</v>
       </c>
       <c r="B38" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>135294216</v>
       </c>
       <c r="B46" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>135294210</v>
       </c>
       <c r="B47" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>135294875</v>
       </c>
       <c r="B52" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>135295273</v>
       </c>
       <c r="B53" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>135293594</v>
       </c>
       <c r="B54" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>135294219</v>
       </c>
       <c r="B55" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>135294859</v>
       </c>
       <c r="B56" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>135294873</v>
       </c>
       <c r="B57" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>135295267</v>
       </c>
       <c r="B58" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>135294880</v>
       </c>
       <c r="B59" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>135294884</v>
       </c>
       <c r="B60" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         <v>135293592</v>
       </c>
       <c r="B61" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>135294683</v>
       </c>
       <c r="B62" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>135294679</v>
       </c>
       <c r="B63" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>135294695</v>
       </c>
       <c r="B64" t="n">
-        <v>81393</v>
+        <v>81420</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135294689</v>
       </c>
       <c r="B65" t="n">
-        <v>92069</v>
+        <v>92096</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>135294687</v>
       </c>
       <c r="B66" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>135294701</v>
       </c>
       <c r="B67" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135302459</v>
       </c>
       <c r="B68" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>135294692</v>
       </c>
       <c r="B70" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>135294702</v>
       </c>
       <c r="B71" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>135302461</v>
       </c>
       <c r="B72" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>135302462</v>
       </c>
       <c r="B73" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>135302460</v>
       </c>
       <c r="B74" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>135293593</v>
       </c>
       <c r="B89" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>135294678</v>
       </c>
       <c r="B90" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>135294684</v>
       </c>
       <c r="B91" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>135294694</v>
       </c>
       <c r="B92" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         <v>135294697</v>
       </c>
       <c r="B93" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>135294700</v>
       </c>
       <c r="B94" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>135293590</v>
       </c>
       <c r="B95" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>135294685</v>
       </c>
       <c r="B96" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 26954-2022 artfynd.xlsx
+++ b/artfynd/A 26954-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135294705</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>135294214</v>
       </c>
       <c r="B13" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>135294216</v>
       </c>
       <c r="B46" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>135294210</v>
       </c>
       <c r="B47" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>135294689</v>
       </c>
       <c r="B65" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>135294687</v>
       </c>
       <c r="B66" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
